--- a/data/trans_bre/IP09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Edad-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-29,6; 29,3</t>
+          <t>-29,55; 31,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 26,22</t>
+          <t>-17,17; 26,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 58,59</t>
+          <t>-4,78; 56,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 46,13</t>
+          <t>-11,93; 47,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-79,42; 190,2</t>
+          <t>-80,51; 196,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,39; 144,57</t>
+          <t>-45,57; 168,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 656,03</t>
+          <t>-20,26; 590,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 12,8</t>
+          <t>-21,0; 13,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 25,41</t>
+          <t>-12,77; 24,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,24; 2,49</t>
+          <t>-46,03; 3,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 43,7</t>
+          <t>-14,25; 45,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,93; 94,72</t>
+          <t>-74,44; 99,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,15; 162,05</t>
+          <t>-40,43; 147,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,62; 4,21</t>
+          <t>-72,54; 7,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,25; 189,47</t>
+          <t>-36,33; 161,28</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 11,14</t>
+          <t>-41,86; 15,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 34,95</t>
+          <t>-17,15; 33,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-73,58; 11,3</t>
+          <t>-73,25; 4,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 29,48</t>
+          <t>-27,05; 34,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-81,51; 49,46</t>
+          <t>-78,43; 83,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,89; 297,84</t>
+          <t>-46,83; 342,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-81,11; 18,99</t>
+          <t>-81,76; 7,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 97,17</t>
+          <t>-48,91; 142,16</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 33,05</t>
+          <t>-33,36; 31,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,28; 13,15</t>
+          <t>-38,52; 13,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,47; 41,39</t>
+          <t>-29,33; 43,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 47,53</t>
+          <t>-22,22; 43,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-73,79; 171,53</t>
+          <t>-77,55; 162,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,83; 29,36</t>
+          <t>-65,83; 28,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,83; 208,66</t>
+          <t>-58,08; 246,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,14; 421,55</t>
+          <t>-66,61; 338,95</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 5,29</t>
+          <t>-16,19; 7,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 11,57</t>
+          <t>-9,3; 14,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 10,05</t>
+          <t>-20,76; 9,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 29,73</t>
+          <t>-6,82; 30,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-54,18; 22,33</t>
+          <t>-49,43; 33,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,34; 39,18</t>
+          <t>-24,83; 51,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-39,86; 26,04</t>
+          <t>-39,54; 27,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 133,41</t>
+          <t>-19,68; 143,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Edad-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-29,55; 31,24</t>
+          <t>-28,72; 30,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 26,85</t>
+          <t>-17,99; 25,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 56,03</t>
+          <t>-5,41; 54,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 47,08</t>
+          <t>-9,91; 48,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-80,51; 196,67</t>
+          <t>-74,06; 195,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-45,57; 168,92</t>
+          <t>-45,04; 153,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 590,03</t>
+          <t>-25,02; 553,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,0; 13,27</t>
+          <t>-20,25; 12,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 24,02</t>
+          <t>-11,86; 26,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,03; 3,52</t>
+          <t>-44,47; 3,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 45,53</t>
+          <t>-14,7; 44,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,44; 99,2</t>
+          <t>-73,04; 108,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 147,87</t>
+          <t>-38,42; 164,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,54; 7,05</t>
+          <t>-70,07; 10,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,33; 161,28</t>
+          <t>-33,07; 176,61</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 15,04</t>
+          <t>-42,45; 14,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 33,32</t>
+          <t>-19,86; 32,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-73,25; 4,5</t>
+          <t>-74,2; 9,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 34,83</t>
+          <t>-25,48; 30,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-78,43; 83,94</t>
+          <t>-81,91; 68,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,83; 342,83</t>
+          <t>-51,45; 262,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-81,76; 7,24</t>
+          <t>-84,75; 18,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,91; 142,16</t>
+          <t>-47,67; 104,16</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 31,04</t>
+          <t>-29,47; 33,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,52; 13,78</t>
+          <t>-41,94; 14,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 43,19</t>
+          <t>-28,3; 39,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,22; 43,51</t>
+          <t>-17,63; 46,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,55; 162,86</t>
+          <t>-77,32; 154,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,83; 28,65</t>
+          <t>-64,27; 34,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,08; 246,76</t>
+          <t>-56,91; 205,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,61; 338,95</t>
+          <t>-58,65; 524,81</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 7,57</t>
+          <t>-18,16; 6,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 14,19</t>
+          <t>-9,98; 12,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 9,82</t>
+          <t>-22,23; 10,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 30,64</t>
+          <t>-6,27; 28,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,43; 33,17</t>
+          <t>-53,53; 28,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 51,69</t>
+          <t>-26,18; 46,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-39,54; 27,42</t>
+          <t>-41,37; 26,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 143,75</t>
+          <t>-16,84; 127,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,68</t>
+          <t>18,48</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>207,93%</t>
+          <t>205,51%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 30,81</t>
+          <t>-29,6; 29,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 25,74</t>
+          <t>-18,3; 26,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 54,92</t>
+          <t>-5,07; 58,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 48,74</t>
+          <t>-12,43; 45,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-74,06; 195,1</t>
+          <t>-79,42; 190,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-45,04; 153,19</t>
+          <t>-48,39; 144,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 553,81</t>
+          <t>-17,57; 656,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,08</t>
+          <t>14,82</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 12,99</t>
+          <t>-19,73; 12,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 26,19</t>
+          <t>-12,04; 25,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,47; 3,16</t>
+          <t>-46,24; 2,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 44,61</t>
+          <t>-13,96; 43,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,04; 108,01</t>
+          <t>-71,93; 94,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 164,61</t>
+          <t>-37,15; 162,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,07; 10,36</t>
+          <t>-70,62; 4,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,07; 176,61</t>
+          <t>-34,06; 183,94</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>1,86</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-42,45; 14,03</t>
+          <t>-41,36; 11,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 32,75</t>
+          <t>-19,44; 34,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-74,2; 9,8</t>
+          <t>-73,58; 11,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,48; 30,19</t>
+          <t>-28,9; 27,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-81,91; 68,17</t>
+          <t>-81,51; 49,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-51,45; 262,67</t>
+          <t>-49,89; 297,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-84,75; 18,18</t>
+          <t>-81,11; 18,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,67; 104,16</t>
+          <t>-52,52; 85,02</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,54</t>
+          <t>-7,8</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>-29,45%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 33,58</t>
+          <t>-29,13; 33,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,94; 14,97</t>
+          <t>-39,28; 13,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 39,36</t>
+          <t>-30,47; 41,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 46,21</t>
+          <t>-27,04; 14,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,32; 154,73</t>
+          <t>-73,79; 171,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,27; 34,73</t>
+          <t>-62,83; 29,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-56,91; 205,04</t>
+          <t>-61,83; 208,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,65; 524,81</t>
+          <t>-71,89; 105,07</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,18</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 6,31</t>
+          <t>-18,11; 5,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 12,91</t>
+          <t>-12,28; 11,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 10,42</t>
+          <t>-20,83; 10,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 28,67</t>
+          <t>-12,18; 16,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-53,53; 28,79</t>
+          <t>-54,18; 22,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 46,77</t>
+          <t>-30,34; 39,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-41,37; 26,34</t>
+          <t>-39,86; 26,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 127,28</t>
+          <t>-31,07; 71,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP09-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,6</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26,38</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18,48</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>111,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>205,51%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.1054385643994959</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.598719941893735</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>26.37572771476744</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>18.4824631866519</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.003564437187317874</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1222090590164172</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.109981553643145</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>2.05509496642354</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-29,6; 29,3</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-18,3; 26,22</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,07; 58,59</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-12,43; 45,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-79,42; 190,2</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-48,39; 144,57</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-17,57; 656,03</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-29.59647203933747</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-18.2969918897607</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.069336532751461</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-12.42809530643464</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.7942440259957607</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.4838845986409674</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1757264551311095</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>29.30142853351704</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>26.21586850731451</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>58.59296651218057</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>45.00486636815558</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.901967727157692</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.445665246731654</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>6.560251035962444</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-5,06</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6,25</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-22,1</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,82</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-24,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>24,59%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-39,78%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40,13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-19,73; 12,8</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-12,04; 25,41</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-46,24; 2,49</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-13,96; 43,79</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-71,93; 94,72</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-37,15; 162,05</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-70,62; 4,21</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-34,06; 183,94</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-5.063242578839172</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6.251504822232457</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-22.10499265896729</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>14.82427774352958</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2404344700295289</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.2459141779972424</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.3977683284853554</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.4013077559083579</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-15,89</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9,47</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-36,63</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,86</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-38,84%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>37,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-47,91%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-19.73410945834393</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-12.04040692507555</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-46.24314675629174</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-13.95996947654579</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.7192865939154326</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3715273159502367</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.7062273543927828</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3406057755639507</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-41,36; 11,14</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-19,44; 34,95</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-73,58; 11,3</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-28,9; 27,11</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-81,51; 49,46</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-49,89; 297,84</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-81,11; 18,99</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-52,52; 85,02</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>12.80287343953434</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>25.40549152717814</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.487071525879251</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>43.79430788851707</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.947215425746457</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.620494554826253</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.04212962025670988</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.839378380146818</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +815,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,7</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-14,46</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,11</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-7,8</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-5,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-26,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-29,45%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-15.88708199616327</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>9.466163142113276</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-36.62842157338563</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.858572787744889</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.3883953933768464</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.3748178572281732</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.4790874295499928</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.0420582470383241</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-29,13; 33,05</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-39,28; 13,15</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-30,47; 41,39</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-27,04; 14,7</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-73,79; 171,53</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-62,83; 29,36</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-61,83; 208,66</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-71,89; 105,07</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-41.36361757444089</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-19.4416689287599</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-73.58228528606369</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-28.89927908576835</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.81505546304708</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4989496627056332</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.811092189987792</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5251721743599849</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>11.13721221296993</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>34.94669226135411</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>11.29557259362264</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>27.11053900707694</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.4946010591188306</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>2.97840750440754</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.1898991086542628</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.8501991943123124</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.699152587445552</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-14.46395670017069</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>6.11469528261312</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-7.79807490426328</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.05120643031333897</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2608460292433625</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.1594666505642243</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2945268139232011</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-29.13086378504869</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-39.27997392460203</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-30.46645408622314</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-27.03656154687399</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.7378881752432562</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.628319116827226</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6183480460814961</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.7189098156529486</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>33.05388174051206</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>13.14559809635097</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>41.38818908643049</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>14.69709362150837</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.715256363352013</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.293581128304902</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.086565322976964</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.050715498626531</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-6,04</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,82</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-5,73</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-20,97%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-12,4%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-18,11; 5,29</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-12,28; 11,57</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-20,83; 10,05</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-12,18; 16,65</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-54,18; 22,33</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-30,34; 39,18</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-39,86; 26,04</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-31,07; 71,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-6.040741411813774</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.8242902565791188</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-5.730119388064531</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.648246004663834</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2097490543700615</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.0246476801954528</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1239927707521249</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.05291615679989517</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-18.10511986856548</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-12.27504825643769</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-20.82886854121656</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-12.17984721302253</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.5417869167199165</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3033766220092579</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.3985723486115914</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3107259689036321</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.285040659027121</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>11.573702933456</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>10.0541918296175</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>16.65264557246027</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.2232633405784972</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3918261493632707</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.2603526425477261</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.7183602933250477</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1113,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
